--- a/param_config.xlsx
+++ b/param_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2099873C-2406-4517-AE14-9B92B92FABB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0C2678-EB0E-4FF2-BD6A-49BAFB35BEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A398E9E3-3C64-4773-A721-4063DF435995}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Parameter</t>
   </si>
@@ -44,6 +44,10 @@
   </si>
   <si>
     <t>NP_Ratio</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1015,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BC71E5-178E-47BF-B16A-45B584891FDB}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
@@ -1054,35 +1058,52 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="D3">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>50</v>
+      </c>
+      <c r="C4">
+        <v>98</v>
+      </c>
+      <c r="D4">
+        <v>85</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>1.5</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>0.01</v>
       </c>
     </row>

--- a/param_config.xlsx
+++ b/param_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0C2678-EB0E-4FF2-BD6A-49BAFB35BEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25EF331-F61E-49CC-B831-62F513E6CF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A398E9E3-3C64-4773-A721-4063DF435995}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Parameter</t>
   </si>
@@ -47,6 +47,10 @@
   </si>
   <si>
     <t>Capacity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Example</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1019,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BC71E5-178E-47BF-B16A-45B584891FDB}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
@@ -1092,18 +1096,35 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>1000</v>
+      </c>
+      <c r="C5">
+        <v>2000</v>
+      </c>
+      <c r="D5">
+        <v>1200</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>1.5</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>0.01</v>
       </c>
     </row>

--- a/param_config.xlsx
+++ b/param_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25EF331-F61E-49CC-B831-62F513E6CF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB85C2B-0411-423B-B497-37D1CF41FB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A398E9E3-3C64-4773-A721-4063DF435995}"/>
   </bookViews>
@@ -37,20 +37,22 @@
     <t>Step</t>
   </si>
   <si>
-    <t>Loading</t>
-  </si>
-  <si>
-    <t>ICE</t>
-  </si>
-  <si>
     <t>NP_Ratio</t>
   </si>
   <si>
-    <t>Capacity</t>
+    <t>Loading (mg/cm2)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Example</t>
+    <t>Capacity (mAh/g)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICE (%)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Example (kkk)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1025,6 +1027,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BC71E5-178E-47BF-B16A-45B584891FDB}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -1045,7 +1050,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -1062,7 +1067,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -1079,7 +1084,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>50</v>
@@ -1113,7 +1118,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/param_config.xlsx
+++ b/param_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB85C2B-0411-423B-B497-37D1CF41FB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A5A3D5-57CC-46FA-A5F9-3273A6EDACEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A398E9E3-3C64-4773-A721-4063DF435995}"/>
+    <workbookView xWindow="8856" yWindow="0" windowWidth="14184" windowHeight="11664" xr2:uid="{A398E9E3-3C64-4773-A721-4063DF435995}"/>
   </bookViews>
   <sheets>
     <sheet name="param_config" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Parameter</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>Min</t>
   </si>
@@ -31,36 +28,83 @@
     <t>Max</t>
   </si>
   <si>
-    <t>Default</t>
-  </si>
-  <si>
     <t>Step</t>
   </si>
   <si>
-    <t>NP_Ratio</t>
-  </si>
-  <si>
-    <t>Loading (mg/cm2)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Capacity (mAh/g)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ICE (%)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Example (kkk)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>Parameter_ID</t>
+  </si>
+  <si>
+    <t>Label_Name</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>loading</t>
+  </si>
+  <si>
+    <t>Cathode Loading</t>
+  </si>
+  <si>
+    <t>mg/cm²</t>
+  </si>
+  <si>
+    <t>양극 로딩량 (가장 중요한 변수)</t>
+  </si>
+  <si>
+    <t>np_ratio</t>
+  </si>
+  <si>
+    <t>N/P Ratio</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>양극 대비 음극 용량 비율</t>
+  </si>
+  <si>
+    <t>cat_density</t>
+  </si>
+  <si>
+    <t>Cathode Density</t>
+  </si>
+  <si>
+    <t>g/cc</t>
+  </si>
+  <si>
+    <t>양극 합제밀도</t>
+  </si>
+  <si>
+    <t>ano_density</t>
+  </si>
+  <si>
+    <t>Anode Density</t>
+  </si>
+  <si>
+    <t>음극 합제밀도 (하드카본 특성 반영)</t>
+  </si>
+  <si>
+    <t>active_ratio</t>
+  </si>
+  <si>
+    <t>Active Material</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>활물질 비율</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +263,12 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -646,9 +696,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1025,112 +1078,150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BC71E5-178E-47BF-B16A-45B584891FDB}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" customWidth="1"/>
+    <col min="7" max="7" width="32.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
+    <row r="2" spans="1:7" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>40</v>
-      </c>
-      <c r="D2">
+      <c r="E2" s="1">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
+      <c r="D3" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="F4" s="1">
         <v>0.1</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>100</v>
-      </c>
-      <c r="C3">
-        <v>200</v>
-      </c>
-      <c r="D3">
-        <v>120</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>50</v>
-      </c>
-      <c r="C4">
-        <v>98</v>
-      </c>
-      <c r="D4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1">
         <v>85</v>
       </c>
-      <c r="E4">
+      <c r="E6" s="1">
+        <v>99</v>
+      </c>
+      <c r="F6" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>1000</v>
-      </c>
-      <c r="C5">
-        <v>2000</v>
-      </c>
-      <c r="D5">
-        <v>1200</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1.5</v>
-      </c>
-      <c r="D6">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="E6">
-        <v>0.01</v>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/param_config.xlsx
+++ b/param_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A5A3D5-57CC-46FA-A5F9-3273A6EDACEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF53BEE-3EAB-4142-91FF-A0A7C117BAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8856" yWindow="0" windowWidth="14184" windowHeight="11664" xr2:uid="{A398E9E3-3C64-4773-A721-4063DF435995}"/>
+    <workbookView xWindow="8820" yWindow="576" windowWidth="14184" windowHeight="11664" xr2:uid="{A398E9E3-3C64-4773-A721-4063DF435995}"/>
   </bookViews>
   <sheets>
     <sheet name="param_config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Min</t>
   </si>
@@ -37,74 +37,44 @@
     <t>Label_Name</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>loading</t>
   </si>
   <si>
-    <t>Cathode Loading</t>
-  </si>
-  <si>
-    <t>mg/cm²</t>
-  </si>
-  <si>
-    <t>양극 로딩량 (가장 중요한 변수)</t>
-  </si>
-  <si>
     <t>np_ratio</t>
   </si>
   <si>
-    <t>N/P Ratio</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>양극 대비 음극 용량 비율</t>
-  </si>
-  <si>
     <t>cat_density</t>
   </si>
   <si>
-    <t>Cathode Density</t>
-  </si>
-  <si>
-    <t>g/cc</t>
-  </si>
-  <si>
-    <t>양극 합제밀도</t>
-  </si>
-  <si>
     <t>ano_density</t>
   </si>
   <si>
-    <t>Anode Density</t>
-  </si>
-  <si>
-    <t>음극 합제밀도 (하드카본 특성 반영)</t>
-  </si>
-  <si>
     <t>active_ratio</t>
   </si>
   <si>
-    <t>Active Material</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>활물질 비율</t>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Cathode Loading (mg/cm2)</t>
+  </si>
+  <si>
+    <t>NP_Ratio</t>
+  </si>
+  <si>
+    <t>Cathode Press Density (g/cc)</t>
+  </si>
+  <si>
+    <t>Anode Press Density (g/cc)</t>
+  </si>
+  <si>
+    <t>Active Material Ratio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,6 +240,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -452,7 +429,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -567,6 +544,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -696,11 +688,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1078,15 +1073,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BC71E5-178E-47BF-B16A-45B584891FDB}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.796875" customWidth="1"/>
     <col min="2" max="2" width="12.796875" customWidth="1"/>
-    <col min="7" max="7" width="32.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1094,134 +1088,116 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="42" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.01</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+    <row r="4" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1">
-        <v>30</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1.05</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="E4" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1">
-        <v>85</v>
-      </c>
-      <c r="E6" s="1">
-        <v>99</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>25</v>
+      <c r="C6" s="2">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2">
+        <v>100</v>
+      </c>
+      <c r="E6" s="2">
+        <v>90</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/param_config.xlsx
+++ b/param_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WS Choi\SynoCore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF53BEE-3EAB-4142-91FF-A0A7C117BAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D30222-20A4-4EEA-A573-AC2C2FEACC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8820" yWindow="576" windowWidth="14184" windowHeight="11664" xr2:uid="{A398E9E3-3C64-4773-A721-4063DF435995}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A398E9E3-3C64-4773-A721-4063DF435995}"/>
   </bookViews>
   <sheets>
     <sheet name="param_config" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Min</t>
   </si>
@@ -55,19 +55,34 @@
     <t>Default</t>
   </si>
   <si>
-    <t>Cathode Loading (mg/cm2)</t>
-  </si>
-  <si>
-    <t>NP_Ratio</t>
-  </si>
-  <si>
-    <t>Cathode Press Density (g/cc)</t>
-  </si>
-  <si>
-    <t>Anode Press Density (g/cc)</t>
-  </si>
-  <si>
-    <t>Active Material Ratio</t>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Cathode Loading</t>
+  </si>
+  <si>
+    <t>mg/cm2</t>
+  </si>
+  <si>
+    <t>N/P Ratio</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Cathode Density</t>
+  </si>
+  <si>
+    <t>g/cc</t>
+  </si>
+  <si>
+    <t>Anode Density</t>
+  </si>
+  <si>
+    <t>Active Material</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
@@ -1073,14 +1088,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BC71E5-178E-47BF-B16A-45B584891FDB}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.796875" customWidth="1"/>
     <col min="2" max="2" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1088,115 +1103,133 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="42" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2">
         <v>5</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>40</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>13</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>1.5</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>1.1499999999999999</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>0.01</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2">
         <v>1.5</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>4</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>2.5</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2">
         <v>0.8</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>2</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="2">
-        <v>0.1</v>
+      <c r="G5" s="2">
+        <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2">
         <v>80</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>100</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>90</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>1</v>
       </c>
     </row>
